--- a/samples/G_科目余额表.xlsx
+++ b/samples/G_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
